--- a/Result/profitability/8064.xlsx
+++ b/Result/profitability/8064.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.47375</v>
+        <v>0.465</v>
       </c>
       <c r="N2" t="n">
-        <v>26.0275</v>
+        <v>26.51375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49625</v>
+        <v>0.485</v>
       </c>
       <c r="N3" t="n">
-        <v>26.045</v>
+        <v>26.755</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.58</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>26.31</v>
+        <v>30.91875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64875</v>
+        <v>0.69125</v>
       </c>
       <c r="N5" t="n">
-        <v>29.1475</v>
+        <v>29.1125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67125</v>
+        <v>0.6125</v>
       </c>
       <c r="N6" t="n">
-        <v>29.46875</v>
+        <v>28.89625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4275</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>25.3725</v>
+        <v>24.40375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.11</v>
+        <v>0.08874999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>20.13</v>
+        <v>20.885</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.4737500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>9.353749999999998</v>
+        <v>9.35375</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8064</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>554</v>
+      </c>
+      <c r="D75" t="n">
+        <v>384</v>
+      </c>
+      <c r="E75" t="n">
+        <v>170</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>33</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.71625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4857142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2449310624493106</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2800000000000011</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.009038089089735357</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
